--- a/agriculture 18.xlsx
+++ b/agriculture 18.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="39">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="40">
   <si>
     <t xml:space="preserve">Year</t>
   </si>
@@ -134,6 +134,9 @@
   </si>
   <si>
     <t xml:space="preserve"> 2019-20</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Unit:- </t>
   </si>
   <si>
     <t xml:space="preserve">Source: Directorate of Economics and Statistics (1997-2020)</t>
@@ -148,7 +151,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]0;\(0\)"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -176,6 +179,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -241,13 +250,13 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="9">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
@@ -258,11 +267,23 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="false" hidden="false"/>
     </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
+      <protection locked="false" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="false" hidden="false"/>
     </xf>
@@ -283,10 +304,10 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:AB1048576"/>
-  <sheetFormatPr defaultColWidth="10.78515625" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <dimension ref="A1:AB26"/>
+  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -337,64 +358,64 @@
       <c r="A2" s="3" t="s">
         <v>15</v>
       </c>
-      <c r="B2" s="1"/>
-      <c r="C2" s="1"/>
-      <c r="D2" s="1"/>
-      <c r="E2" s="1"/>
-      <c r="F2" s="1"/>
-      <c r="G2" s="1"/>
-      <c r="H2" s="1"/>
-      <c r="I2" s="1"/>
-      <c r="J2" s="1"/>
-      <c r="K2" s="1"/>
-      <c r="L2" s="1"/>
-      <c r="M2" s="1"/>
-      <c r="N2" s="1"/>
+      <c r="B2" s="4"/>
+      <c r="C2" s="4"/>
+      <c r="D2" s="4"/>
+      <c r="E2" s="4"/>
+      <c r="F2" s="4"/>
+      <c r="G2" s="4"/>
+      <c r="H2" s="4"/>
+      <c r="I2" s="4"/>
+      <c r="J2" s="4"/>
+      <c r="K2" s="4"/>
+      <c r="L2" s="4"/>
+      <c r="M2" s="4"/>
+      <c r="N2" s="4"/>
     </row>
     <row r="3" customFormat="false" ht="14.4" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="B3" s="4" t="n">
+      <c r="B3" s="5" t="n">
         <v>30.8981233243968</v>
       </c>
-      <c r="C3" s="4" t="n">
+      <c r="C3" s="5" t="n">
         <v>-20.427687113112</v>
       </c>
-      <c r="D3" s="4" t="n">
+      <c r="D3" s="5" t="n">
         <v>-37.9173740803622</v>
       </c>
-      <c r="E3" s="4" t="n">
+      <c r="E3" s="5" t="n">
         <v>3.2258064516129</v>
       </c>
-      <c r="F3" s="4" t="n">
+      <c r="F3" s="5" t="n">
         <v>-25.9905977165883</v>
       </c>
-      <c r="G3" s="4" t="n">
+      <c r="G3" s="5" t="n">
         <v>57.0191382444136</v>
       </c>
-      <c r="H3" s="4" t="n">
+      <c r="H3" s="5" t="n">
         <v>-7.89946140035906</v>
       </c>
-      <c r="I3" s="4" t="n">
+      <c r="I3" s="5" t="n">
         <v>-12.1414913957935</v>
       </c>
-      <c r="J3" s="4" t="n">
+      <c r="J3" s="5" t="n">
         <v>52.962962962963</v>
       </c>
-      <c r="K3" s="4" t="n">
+      <c r="K3" s="5" t="n">
         <v>72.1804511278195</v>
       </c>
-      <c r="L3" s="4" t="n">
+      <c r="L3" s="5" t="n">
         <v>39.6771452846219</v>
       </c>
-      <c r="M3" s="4" t="n">
+      <c r="M3" s="5" t="n">
         <v>4.83964005537609</v>
       </c>
-      <c r="N3" s="4" t="n">
+      <c r="N3" s="5" t="n">
         <v>18.5688405797102</v>
       </c>
-      <c r="O3" s="4" t="n">
+      <c r="O3" s="5" t="n">
         <v>62.2950819672131</v>
       </c>
     </row>
@@ -402,46 +423,46 @@
       <c r="A4" s="3" t="s">
         <v>17</v>
       </c>
-      <c r="B4" s="4" t="n">
+      <c r="B4" s="5" t="n">
         <v>-29.4930875576037</v>
       </c>
-      <c r="C4" s="4" t="n">
+      <c r="C4" s="5" t="n">
         <v>15.5940594059406</v>
       </c>
-      <c r="D4" s="4" t="n">
+      <c r="D4" s="5" t="n">
         <v>-16.8641750227894</v>
       </c>
-      <c r="E4" s="4" t="n">
+      <c r="E4" s="5" t="n">
         <v>-5.46875</v>
       </c>
-      <c r="F4" s="4" t="n">
+      <c r="F4" s="5" t="n">
         <v>-29.491833030853</v>
       </c>
-      <c r="G4" s="4" t="n">
+      <c r="G4" s="5" t="n">
         <v>-53.5986653956149</v>
       </c>
-      <c r="H4" s="4" t="n">
+      <c r="H4" s="5" t="n">
         <v>-11.6959064327485</v>
       </c>
-      <c r="I4" s="4" t="n">
+      <c r="I4" s="5" t="n">
         <v>-38.7377584330794</v>
       </c>
-      <c r="J4" s="4" t="n">
+      <c r="J4" s="5" t="n">
         <v>-0.968523002421306</v>
       </c>
-      <c r="K4" s="4" t="n">
+      <c r="K4" s="5" t="n">
         <v>-20.174672489083</v>
       </c>
-      <c r="L4" s="4" t="n">
+      <c r="L4" s="5" t="n">
         <v>-45.0729927007299</v>
       </c>
-      <c r="M4" s="4" t="n">
+      <c r="M4" s="5" t="n">
         <v>-4.6382393397524</v>
       </c>
-      <c r="N4" s="4" t="n">
+      <c r="N4" s="5" t="n">
         <v>-34.4919786096257</v>
       </c>
-      <c r="O4" s="4" t="n">
+      <c r="O4" s="5" t="n">
         <v>21.8337218337218</v>
       </c>
     </row>
@@ -449,46 +470,46 @@
       <c r="A5" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="B5" s="4" t="n">
+      <c r="B5" s="5" t="n">
         <v>23.8198983297023</v>
       </c>
-      <c r="C5" s="4" t="n">
+      <c r="C5" s="5" t="n">
         <v>13.5821352095442</v>
       </c>
-      <c r="D5" s="4" t="n">
+      <c r="D5" s="5" t="n">
         <v>34.6491228070175</v>
       </c>
-      <c r="E5" s="4" t="n">
+      <c r="E5" s="5" t="n">
         <v>22.7272727272727</v>
       </c>
-      <c r="F5" s="4" t="n">
+      <c r="F5" s="5" t="n">
         <v>48.3912483912484</v>
       </c>
-      <c r="G5" s="4" t="n">
+      <c r="G5" s="5" t="n">
         <v>70.8269131997946</v>
       </c>
-      <c r="H5" s="4" t="n">
+      <c r="H5" s="5" t="n">
         <v>1.32450331125829</v>
       </c>
-      <c r="I5" s="4" t="n">
+      <c r="I5" s="5" t="n">
         <v>-6.57193605683837</v>
       </c>
-      <c r="J5" s="4" t="n">
+      <c r="J5" s="5" t="n">
         <v>-26.8948655256724</v>
       </c>
-      <c r="K5" s="4" t="n">
+      <c r="K5" s="5" t="n">
         <v>15.2078774617068</v>
       </c>
-      <c r="L5" s="4" t="n">
+      <c r="L5" s="5" t="n">
         <v>26.0797342192691</v>
       </c>
-      <c r="M5" s="4" t="n">
+      <c r="M5" s="5" t="n">
         <v>3.36372028617586</v>
       </c>
-      <c r="N5" s="4" t="n">
+      <c r="N5" s="5" t="n">
         <v>46.8804664723032</v>
       </c>
-      <c r="O5" s="4" t="n">
+      <c r="O5" s="5" t="n">
         <v>-21.8112244897959</v>
       </c>
     </row>
@@ -496,46 +517,46 @@
       <c r="A6" s="3" t="s">
         <v>19</v>
       </c>
-      <c r="B6" s="4" t="n">
+      <c r="B6" s="5" t="n">
         <v>-3.6950146627566</v>
       </c>
-      <c r="C6" s="4" t="n">
+      <c r="C6" s="5" t="n">
         <v>15.1360086183679</v>
       </c>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="5" t="n">
         <v>18.485342019544</v>
       </c>
-      <c r="E6" s="4" t="n">
+      <c r="E6" s="5" t="n">
         <v>-34.006734006734</v>
       </c>
-      <c r="F6" s="4" t="n">
+      <c r="F6" s="5" t="n">
         <v>18.9939288811795</v>
       </c>
-      <c r="G6" s="4" t="n">
+      <c r="G6" s="5" t="n">
         <v>5.4892191392492</v>
       </c>
-      <c r="H6" s="4" t="n">
+      <c r="H6" s="5" t="n">
         <v>32.7886710239651</v>
       </c>
-      <c r="I6" s="4" t="n">
+      <c r="I6" s="5" t="n">
         <v>11.9771863117871</v>
       </c>
-      <c r="J6" s="4" t="n">
+      <c r="J6" s="5" t="n">
         <v>20.9030100334448</v>
       </c>
-      <c r="K6" s="4" t="n">
+      <c r="K6" s="5" t="n">
         <v>-41.5004748338082</v>
       </c>
-      <c r="L6" s="4" t="n">
+      <c r="L6" s="5" t="n">
         <v>19.5432586736935</v>
       </c>
-      <c r="M6" s="4" t="n">
+      <c r="M6" s="5" t="n">
         <v>-26.9718113312866</v>
       </c>
-      <c r="N6" s="4" t="n">
+      <c r="N6" s="5" t="n">
         <v>-12.4255657006749</v>
       </c>
-      <c r="O6" s="4" t="n">
+      <c r="O6" s="5" t="n">
         <v>12.2349102773246</v>
       </c>
     </row>
@@ -543,46 +564,46 @@
       <c r="A7" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="B7" s="4" t="n">
+      <c r="B7" s="5" t="n">
         <v>9.01339829476249</v>
       </c>
-      <c r="C7" s="4" t="n">
+      <c r="C7" s="5" t="n">
         <v>-24.327485380117</v>
       </c>
-      <c r="D7" s="4" t="n">
+      <c r="D7" s="5" t="n">
         <v>-15.3951890034364</v>
       </c>
-      <c r="E7" s="4" t="n">
+      <c r="E7" s="5" t="n">
         <v>-11.2244897959184</v>
       </c>
-      <c r="F7" s="4" t="n">
+      <c r="F7" s="5" t="n">
         <v>4.66472303206997</v>
       </c>
-      <c r="G7" s="4" t="n">
+      <c r="G7" s="5" t="n">
         <v>44.6824104234528</v>
       </c>
-      <c r="H7" s="4" t="n">
+      <c r="H7" s="5" t="n">
         <v>-3.93765381460214</v>
       </c>
-      <c r="I7" s="4" t="n">
+      <c r="I7" s="5" t="n">
         <v>33.616298811545</v>
       </c>
-      <c r="J7" s="4" t="n">
+      <c r="J7" s="5" t="n">
         <v>7.60719225449515</v>
       </c>
-      <c r="K7" s="4" t="n">
+      <c r="K7" s="5" t="n">
         <v>58.9285714285714</v>
       </c>
-      <c r="L7" s="4" t="n">
+      <c r="L7" s="5" t="n">
         <v>-35.1579720793534</v>
       </c>
-      <c r="M7" s="4" t="n">
+      <c r="M7" s="5" t="n">
         <v>-7.78873347091645</v>
       </c>
-      <c r="N7" s="4" t="n">
+      <c r="N7" s="5" t="n">
         <v>-1.13327289211242</v>
       </c>
-      <c r="O7" s="4" t="n">
+      <c r="O7" s="5" t="n">
         <v>49.1279069767442</v>
       </c>
     </row>
@@ -590,46 +611,46 @@
       <c r="A8" s="3" t="s">
         <v>21</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="5" t="n">
         <v>-1.7877094972067</v>
       </c>
-      <c r="C8" s="4" t="n">
+      <c r="C8" s="5" t="n">
         <v>2.0401854714065</v>
       </c>
-      <c r="D8" s="4" t="n">
+      <c r="D8" s="5" t="n">
         <v>10.1543460601137</v>
       </c>
-      <c r="E8" s="4" t="n">
+      <c r="E8" s="5" t="n">
         <v>-4.02298850574713</v>
       </c>
-      <c r="F8" s="4" t="n">
+      <c r="F8" s="5" t="n">
         <v>25.4178272980501</v>
       </c>
-      <c r="G8" s="4" t="n">
+      <c r="G8" s="5" t="n">
         <v>2.48494399729837</v>
       </c>
-      <c r="H8" s="4" t="n">
+      <c r="H8" s="5" t="n">
         <v>-5.46541417591802</v>
       </c>
-      <c r="I8" s="4" t="n">
+      <c r="I8" s="5" t="n">
         <v>31.130876747141</v>
       </c>
-      <c r="J8" s="4" t="n">
+      <c r="J8" s="5" t="n">
         <v>12.4678663239075</v>
       </c>
-      <c r="K8" s="4" t="n">
+      <c r="K8" s="5" t="n">
         <v>3.57507660878447</v>
       </c>
-      <c r="L8" s="4" t="n">
+      <c r="L8" s="5" t="n">
         <v>1.98300283286119</v>
       </c>
-      <c r="M8" s="4" t="n">
+      <c r="M8" s="5" t="n">
         <v>0.903514588859422</v>
       </c>
-      <c r="N8" s="4" t="n">
+      <c r="N8" s="5" t="n">
         <v>-6.51077487391105</v>
       </c>
-      <c r="O8" s="4" t="n">
+      <c r="O8" s="5" t="n">
         <v>4.09356725146199</v>
       </c>
     </row>
@@ -637,46 +658,46 @@
       <c r="A9" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="B9" s="4" t="n">
+      <c r="B9" s="5" t="n">
         <v>15.358361774744</v>
       </c>
-      <c r="C9" s="4" t="n">
+      <c r="C9" s="5" t="n">
         <v>13.3898818539836</v>
       </c>
-      <c r="D9" s="4" t="n">
+      <c r="D9" s="5" t="n">
         <v>-2.06489675516224</v>
       </c>
-      <c r="E9" s="4" t="n">
+      <c r="E9" s="5" t="n">
         <v>8.38323353293413</v>
       </c>
-      <c r="F9" s="4" t="n">
+      <c r="F9" s="5" t="n">
         <v>15.1582454192116</v>
       </c>
-      <c r="G9" s="4" t="n">
+      <c r="G9" s="5" t="n">
         <v>6.50794958398551</v>
       </c>
-      <c r="H9" s="4" t="n">
+      <c r="H9" s="5" t="n">
         <v>-8.40108401084011</v>
       </c>
-      <c r="I9" s="4" t="n">
+      <c r="I9" s="5" t="n">
         <v>9.10852713178294</v>
       </c>
-      <c r="J9" s="4" t="n">
+      <c r="J9" s="5" t="n">
         <v>13.2571428571429</v>
       </c>
-      <c r="K9" s="4" t="n">
+      <c r="K9" s="5" t="n">
         <v>13.0177514792899</v>
       </c>
-      <c r="L9" s="4" t="n">
+      <c r="L9" s="5" t="n">
         <v>7.44444444444445</v>
       </c>
-      <c r="M9" s="4" t="n">
+      <c r="M9" s="5" t="n">
         <v>14.1624907582354</v>
       </c>
-      <c r="N9" s="4" t="n">
+      <c r="N9" s="5" t="n">
         <v>15.6449239823443</v>
       </c>
-      <c r="O9" s="4" t="n">
+      <c r="O9" s="5" t="n">
         <v>-5.66479400749064</v>
       </c>
     </row>
@@ -684,46 +705,46 @@
       <c r="A10" s="3" t="s">
         <v>23</v>
       </c>
-      <c r="B10" s="4" t="n">
+      <c r="B10" s="5" t="n">
         <v>-15.6804733727811</v>
       </c>
-      <c r="C10" s="4" t="n">
+      <c r="C10" s="5" t="n">
         <v>23.5639861074005</v>
       </c>
-      <c r="D10" s="4" t="n">
+      <c r="D10" s="5" t="n">
         <v>6.85240963855422</v>
       </c>
-      <c r="E10" s="4" t="n">
+      <c r="E10" s="5" t="n">
         <v>-2.20994475138122</v>
       </c>
-      <c r="F10" s="4" t="n">
+      <c r="F10" s="5" t="n">
         <v>-18.2738669238187</v>
       </c>
-      <c r="G10" s="4" t="n">
+      <c r="G10" s="5" t="n">
         <v>34.2279629772862</v>
       </c>
-      <c r="H10" s="4" t="n">
+      <c r="H10" s="5" t="n">
         <v>25.6410256410256</v>
       </c>
-      <c r="I10" s="4" t="n">
+      <c r="I10" s="5" t="n">
         <v>13.854351687389</v>
       </c>
-      <c r="J10" s="4" t="n">
+      <c r="J10" s="5" t="n">
         <v>13.9253279515641</v>
       </c>
-      <c r="K10" s="4" t="n">
+      <c r="K10" s="5" t="n">
         <v>27.0506108202443</v>
       </c>
-      <c r="L10" s="4" t="n">
+      <c r="L10" s="5" t="n">
         <v>-3.36091003102379</v>
       </c>
-      <c r="M10" s="4" t="n">
+      <c r="M10" s="5" t="n">
         <v>-17.3706555371663</v>
       </c>
-      <c r="N10" s="4" t="n">
+      <c r="N10" s="5" t="n">
         <v>16.0517387616624</v>
       </c>
-      <c r="O10" s="4" t="n">
+      <c r="O10" s="5" t="n">
         <v>-3.2258064516129</v>
       </c>
     </row>
@@ -731,46 +752,46 @@
       <c r="A11" s="3" t="s">
         <v>24</v>
       </c>
-      <c r="B11" s="4" t="n">
+      <c r="B11" s="5" t="n">
         <v>-15.2046783625731</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="5" t="n">
         <v>-31.7189189189189</v>
       </c>
-      <c r="D11" s="4" t="n">
+      <c r="D11" s="5" t="n">
         <v>1.05708245243128</v>
       </c>
-      <c r="E11" s="4" t="n">
+      <c r="E11" s="5" t="n">
         <v>31.0734463276836</v>
       </c>
-      <c r="F11" s="4" t="n">
+      <c r="F11" s="5" t="n">
         <v>3.48082595870207</v>
       </c>
-      <c r="G11" s="4" t="n">
+      <c r="G11" s="5" t="n">
         <v>-32.1994506655398</v>
       </c>
-      <c r="H11" s="4" t="n">
+      <c r="H11" s="5" t="n">
         <v>-11.0675039246468</v>
       </c>
-      <c r="I11" s="4" t="n">
+      <c r="I11" s="5" t="n">
         <v>-21.5288611544462</v>
       </c>
-      <c r="J11" s="4" t="n">
+      <c r="J11" s="5" t="n">
         <v>28.1665190434012</v>
       </c>
-      <c r="K11" s="4" t="n">
+      <c r="K11" s="5" t="n">
         <v>-23.489010989011</v>
       </c>
-      <c r="L11" s="4" t="n">
+      <c r="L11" s="5" t="n">
         <v>-29.7485286249331</v>
       </c>
-      <c r="M11" s="4" t="n">
+      <c r="M11" s="5" t="n">
         <v>-14.4126099451363</v>
       </c>
-      <c r="N11" s="4" t="n">
+      <c r="N11" s="5" t="n">
         <v>-42.6457153298008</v>
       </c>
-      <c r="O11" s="4" t="n">
+      <c r="O11" s="5" t="n">
         <v>0.358974358974362</v>
       </c>
     </row>
@@ -778,46 +799,46 @@
       <c r="A12" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="B12" s="4" t="n">
+      <c r="B12" s="5" t="n">
         <v>-1.86206896551724</v>
       </c>
-      <c r="C12" s="4" t="n">
+      <c r="C12" s="5" t="n">
         <v>-36.0987967067764</v>
       </c>
-      <c r="D12" s="4" t="n">
+      <c r="D12" s="5" t="n">
         <v>-16.9456066945607</v>
       </c>
-      <c r="E12" s="4" t="n">
+      <c r="E12" s="5" t="n">
         <v>-10.7758620689655</v>
       </c>
-      <c r="F12" s="4" t="n">
+      <c r="F12" s="5" t="n">
         <v>-8.49486887115165</v>
       </c>
-      <c r="G12" s="4" t="n">
+      <c r="G12" s="5" t="n">
         <v>-33.9613020198872</v>
       </c>
-      <c r="H12" s="4" t="n">
+      <c r="H12" s="5" t="n">
         <v>-12.180052956752</v>
       </c>
-      <c r="I12" s="4" t="n">
+      <c r="I12" s="5" t="n">
         <v>-19.3836978131213</v>
       </c>
-      <c r="J12" s="4" t="n">
+      <c r="J12" s="5" t="n">
         <v>-31.9281271596406</v>
       </c>
-      <c r="K12" s="4" t="n">
+      <c r="K12" s="5" t="n">
         <v>-8.97666068222621</v>
       </c>
-      <c r="L12" s="4" t="n">
+      <c r="L12" s="5" t="n">
         <v>-32.6732673267327</v>
       </c>
-      <c r="M12" s="4" t="n">
+      <c r="M12" s="5" t="n">
         <v>-58.6894586894587</v>
       </c>
-      <c r="N12" s="4" t="n">
+      <c r="N12" s="5" t="n">
         <v>-40.5861739407455</v>
       </c>
-      <c r="O12" s="4" t="n">
+      <c r="O12" s="5" t="n">
         <v>-19.1108840061318</v>
       </c>
     </row>
@@ -825,46 +846,46 @@
       <c r="A13" s="3" t="s">
         <v>26</v>
       </c>
-      <c r="B13" s="4" t="n">
+      <c r="B13" s="5" t="n">
         <v>-15.6008432888264</v>
       </c>
-      <c r="C13" s="4" t="n">
+      <c r="C13" s="5" t="n">
         <v>-20.0693756194252</v>
       </c>
-      <c r="D13" s="4" t="n">
+      <c r="D13" s="5" t="n">
         <v>-17.2124265323258</v>
       </c>
-      <c r="E13" s="4" t="n">
+      <c r="E13" s="5" t="n">
         <v>-39.1304347826087</v>
       </c>
-      <c r="F13" s="4" t="n">
+      <c r="F13" s="5" t="n">
         <v>-16.0747663551402</v>
       </c>
-      <c r="G13" s="4" t="n">
+      <c r="G13" s="5" t="n">
         <v>-28.3256831538759</v>
       </c>
-      <c r="H13" s="4" t="n">
+      <c r="H13" s="5" t="n">
         <v>-6.73366834170854</v>
       </c>
-      <c r="I13" s="4" t="n">
+      <c r="I13" s="5" t="n">
         <v>3.69913686806411</v>
       </c>
-      <c r="J13" s="4" t="n">
+      <c r="J13" s="5" t="n">
         <v>-11.6751269035533</v>
       </c>
-      <c r="K13" s="4" t="n">
+      <c r="K13" s="5" t="n">
         <v>-41.8145956607495</v>
       </c>
-      <c r="L13" s="4" t="n">
+      <c r="L13" s="5" t="n">
         <v>-6.90045248868778</v>
       </c>
-      <c r="M13" s="4" t="n">
+      <c r="M13" s="5" t="n">
         <v>11.4778325123153</v>
       </c>
-      <c r="N13" s="4" t="n">
+      <c r="N13" s="5" t="n">
         <v>9.70509383378015</v>
       </c>
-      <c r="O13" s="4" t="n">
+      <c r="O13" s="5" t="n">
         <v>-12.4447252053064</v>
       </c>
     </row>
@@ -872,46 +893,46 @@
       <c r="A14" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="B14" s="4" t="n">
+      <c r="B14" s="5" t="n">
         <v>-14.1548709408826</v>
       </c>
-      <c r="C14" s="4" t="n">
+      <c r="C14" s="5" t="n">
         <v>-6.9435833849969</v>
       </c>
-      <c r="D14" s="4" t="n">
+      <c r="D14" s="5" t="n">
         <v>-13.7931034482759</v>
       </c>
-      <c r="E14" s="4" t="n">
+      <c r="E14" s="5" t="n">
         <v>6.34920634920635</v>
       </c>
-      <c r="F14" s="4" t="n">
+      <c r="F14" s="5" t="n">
         <v>-28.2108389012621</v>
       </c>
-      <c r="G14" s="4" t="n">
+      <c r="G14" s="5" t="n">
         <v>52.4539142925545</v>
       </c>
-      <c r="H14" s="4" t="n">
+      <c r="H14" s="5" t="n">
         <v>-14.0086206896552</v>
       </c>
-      <c r="I14" s="4" t="n">
+      <c r="I14" s="5" t="n">
         <v>6.42092746730083</v>
       </c>
-      <c r="J14" s="4" t="n">
+      <c r="J14" s="5" t="n">
         <v>28.8505747126437</v>
       </c>
-      <c r="K14" s="4" t="n">
+      <c r="K14" s="5" t="n">
         <v>-1.52542372881356</v>
       </c>
-      <c r="L14" s="4" t="n">
+      <c r="L14" s="5" t="n">
         <v>22.7217496962333</v>
       </c>
-      <c r="M14" s="4" t="n">
+      <c r="M14" s="5" t="n">
         <v>-0.64074237737517</v>
       </c>
-      <c r="N14" s="4" t="n">
+      <c r="N14" s="5" t="n">
         <v>22.4340175953079</v>
       </c>
-      <c r="O14" s="4" t="n">
+      <c r="O14" s="5" t="n">
         <v>-20.7792207792208</v>
       </c>
     </row>
@@ -919,46 +940,46 @@
       <c r="A15" s="3" t="s">
         <v>28</v>
       </c>
-      <c r="B15" s="4" t="n">
+      <c r="B15" s="5" t="n">
         <v>-8.94131910766246</v>
       </c>
-      <c r="C15" s="4" t="n">
+      <c r="C15" s="5" t="n">
         <v>-12.5938041305796</v>
       </c>
-      <c r="D15" s="4" t="n">
+      <c r="D15" s="5" t="n">
         <v>-7.98823529411764</v>
       </c>
-      <c r="E15" s="4" t="n">
+      <c r="E15" s="5" t="n">
         <v>12.484328358209</v>
       </c>
-      <c r="F15" s="4" t="n">
+      <c r="F15" s="5" t="n">
         <v>-10.3898655635988</v>
       </c>
-      <c r="G15" s="4" t="n">
+      <c r="G15" s="5" t="n">
         <v>21.3857726130653</v>
       </c>
-      <c r="H15" s="4" t="n">
+      <c r="H15" s="5" t="n">
         <v>-10.0537593984962</v>
       </c>
-      <c r="I15" s="4" t="n">
+      <c r="I15" s="5" t="n">
         <v>-31.3448044692737</v>
       </c>
-      <c r="J15" s="4" t="n">
+      <c r="J15" s="5" t="n">
         <v>-14.8987511150758</v>
       </c>
-      <c r="K15" s="4" t="n">
+      <c r="K15" s="5" t="n">
         <v>-17.745438898451</v>
       </c>
-      <c r="L15" s="4" t="n">
+      <c r="L15" s="5" t="n">
         <v>-18.5109900990099</v>
       </c>
-      <c r="M15" s="4" t="n">
+      <c r="M15" s="5" t="n">
         <v>-45.9354458527907</v>
       </c>
-      <c r="N15" s="4" t="n">
+      <c r="N15" s="5" t="n">
         <v>-30.5534930139721</v>
       </c>
-      <c r="O15" s="4" t="n">
+      <c r="O15" s="5" t="n">
         <v>131.235610200364</v>
       </c>
     </row>
@@ -966,46 +987,46 @@
       <c r="A16" s="3" t="s">
         <v>29</v>
       </c>
-      <c r="B16" s="4" t="n">
+      <c r="B16" s="5" t="n">
         <v>5.29380122814398</v>
       </c>
-      <c r="C16" s="4" t="n">
+      <c r="C16" s="5" t="n">
         <v>6.3336958932656</v>
       </c>
-      <c r="D16" s="4" t="n">
+      <c r="D16" s="5" t="n">
         <v>9.823296253676</v>
       </c>
-      <c r="E16" s="4" t="n">
+      <c r="E16" s="5" t="n">
         <v>-9.62721175089069</v>
       </c>
-      <c r="F16" s="4" t="n">
+      <c r="F16" s="5" t="n">
         <v>32.1746506179821</v>
       </c>
-      <c r="G16" s="4" t="n">
+      <c r="G16" s="5" t="n">
         <v>-26.3796587926849</v>
       </c>
-      <c r="H16" s="4" t="n">
+      <c r="H16" s="5" t="n">
         <v>-13.6422340830153</v>
       </c>
-      <c r="I16" s="4" t="n">
+      <c r="I16" s="5" t="n">
         <v>26.3603726174357</v>
       </c>
-      <c r="J16" s="4" t="n">
+      <c r="J16" s="5" t="n">
         <v>-8.81743423638736</v>
       </c>
-      <c r="K16" s="4" t="n">
+      <c r="K16" s="5" t="n">
         <v>8.77047242199711</v>
       </c>
-      <c r="L16" s="4" t="n">
+      <c r="L16" s="5" t="n">
         <v>-25.3170262891552</v>
       </c>
-      <c r="M16" s="4" t="n">
+      <c r="M16" s="5" t="n">
         <v>10.7110936900394</v>
       </c>
-      <c r="N16" s="4" t="n">
+      <c r="N16" s="5" t="n">
         <v>10.8562428325482</v>
       </c>
-      <c r="O16" s="4" t="n">
+      <c r="O16" s="5" t="n">
         <v>-13.638263120395</v>
       </c>
     </row>
@@ -1013,46 +1034,46 @@
       <c r="A17" s="3" t="s">
         <v>30</v>
       </c>
-      <c r="B17" s="4" t="n">
+      <c r="B17" s="5" t="n">
         <v>-11.6856210433034</v>
       </c>
-      <c r="C17" s="4" t="n">
+      <c r="C17" s="5" t="n">
         <v>6.51848697872426</v>
       </c>
-      <c r="D17" s="4" t="n">
+      <c r="D17" s="5" t="n">
         <v>-12.3325820092022</v>
       </c>
-      <c r="E17" s="4" t="n">
+      <c r="E17" s="5" t="n">
         <v>8.64937086141333</v>
       </c>
-      <c r="F17" s="4" t="n">
+      <c r="F17" s="5" t="n">
         <v>2.939494452705</v>
       </c>
-      <c r="G17" s="4" t="n">
+      <c r="G17" s="5" t="n">
         <v>33.6557519155245</v>
       </c>
-      <c r="H17" s="4" t="n">
+      <c r="H17" s="5" t="n">
         <v>1.7986580645994</v>
       </c>
-      <c r="I17" s="4" t="n">
+      <c r="I17" s="5" t="n">
         <v>-25.0424051342089</v>
       </c>
-      <c r="J17" s="4" t="n">
+      <c r="J17" s="5" t="n">
         <v>5.07341343744108</v>
       </c>
-      <c r="K17" s="4" t="n">
+      <c r="K17" s="5" t="n">
         <v>4.26826570324328</v>
       </c>
-      <c r="L17" s="4" t="n">
+      <c r="L17" s="5" t="n">
         <v>78.6324369173703</v>
       </c>
-      <c r="M17" s="4" t="n">
+      <c r="M17" s="5" t="n">
         <v>37.6825054798083</v>
       </c>
-      <c r="N17" s="4" t="n">
+      <c r="N17" s="5" t="n">
         <v>22.68640711353</v>
       </c>
-      <c r="O17" s="4" t="n">
+      <c r="O17" s="5" t="n">
         <v>-27.2128922568381</v>
       </c>
     </row>
@@ -1060,46 +1081,46 @@
       <c r="A18" s="3" t="s">
         <v>31</v>
       </c>
-      <c r="B18" s="4" t="n">
+      <c r="B18" s="5" t="n">
         <v>4.12371134020619</v>
       </c>
-      <c r="C18" s="4" t="n">
+      <c r="C18" s="5" t="n">
         <v>-15.0067294751009</v>
       </c>
-      <c r="D18" s="4" t="n">
+      <c r="D18" s="5" t="n">
         <v>-1.99203187250996</v>
       </c>
-      <c r="E18" s="4" t="n">
+      <c r="E18" s="5" t="n">
         <v>6.75675675675675</v>
       </c>
-      <c r="F18" s="4" t="n">
+      <c r="F18" s="5" t="n">
         <v>-0.593723494486853</v>
       </c>
-      <c r="G18" s="4" t="n">
+      <c r="G18" s="5" t="n">
         <v>-50.5784906652643</v>
       </c>
-      <c r="H18" s="4" t="n">
+      <c r="H18" s="5" t="n">
         <v>-5.07131537242472</v>
       </c>
-      <c r="I18" s="4" t="n">
+      <c r="I18" s="5" t="n">
         <v>-6.18556701030928</v>
       </c>
-      <c r="J18" s="4" t="n">
+      <c r="J18" s="5" t="n">
         <v>21.3347921225383</v>
       </c>
-      <c r="K18" s="4" t="n">
+      <c r="K18" s="5" t="n">
         <v>13.09963099631</v>
       </c>
-      <c r="L18" s="4" t="n">
+      <c r="L18" s="5" t="n">
         <v>-24.9544626593807</v>
       </c>
-      <c r="M18" s="4" t="n">
+      <c r="M18" s="5" t="n">
         <v>-25.7690232056125</v>
       </c>
-      <c r="N18" s="4" t="n">
+      <c r="N18" s="5" t="n">
         <v>-20.4987320371936</v>
       </c>
-      <c r="O18" s="4" t="n">
+      <c r="O18" s="5" t="n">
         <v>13.3458646616541</v>
       </c>
     </row>
@@ -1107,46 +1128,46 @@
       <c r="A19" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="B19" s="4" t="n">
+      <c r="B19" s="5" t="n">
         <v>0.770077007700776</v>
       </c>
-      <c r="C19" s="4" t="n">
+      <c r="C19" s="5" t="n">
         <v>-5.3840063341251</v>
       </c>
-      <c r="D19" s="4" t="n">
+      <c r="D19" s="5" t="n">
         <v>-4.47154471544715</v>
       </c>
-      <c r="E19" s="4" t="n">
+      <c r="E19" s="5" t="n">
         <v>-6.9620253164557</v>
       </c>
-      <c r="F19" s="4" t="n">
+      <c r="F19" s="5" t="n">
         <v>-8.02047781569966</v>
       </c>
-      <c r="G19" s="4" t="n">
+      <c r="G19" s="5" t="n">
         <v>59.0582601755786</v>
       </c>
-      <c r="H19" s="4" t="n">
+      <c r="H19" s="5" t="n">
         <v>-10.016694490818</v>
       </c>
-      <c r="I19" s="4" t="n">
+      <c r="I19" s="5" t="n">
         <v>-8.05860805860806</v>
       </c>
-      <c r="J19" s="4" t="n">
+      <c r="J19" s="5" t="n">
         <v>-12.6239855725879</v>
       </c>
-      <c r="K19" s="4" t="n">
+      <c r="K19" s="5" t="n">
         <v>6.03588907014683</v>
       </c>
-      <c r="L19" s="4" t="n">
+      <c r="L19" s="5" t="n">
         <v>28.1553398058253</v>
       </c>
-      <c r="M19" s="4" t="n">
+      <c r="M19" s="5" t="n">
         <v>74.2639040348964</v>
       </c>
-      <c r="N19" s="4" t="n">
+      <c r="N19" s="5" t="n">
         <v>14.0882509303562</v>
       </c>
-      <c r="O19" s="4" t="n">
+      <c r="O19" s="5" t="n">
         <v>14.8148148148148</v>
       </c>
     </row>
@@ -1154,46 +1175,46 @@
       <c r="A20" s="3" t="s">
         <v>33</v>
       </c>
-      <c r="B20" s="4" t="n">
+      <c r="B20" s="5" t="n">
         <v>6.1051310043668</v>
       </c>
-      <c r="C20" s="4" t="n">
+      <c r="C20" s="5" t="n">
         <v>-8.57179916317992</v>
       </c>
-      <c r="D20" s="4" t="n">
+      <c r="D20" s="5" t="n">
         <v>-14.9700709219858</v>
       </c>
-      <c r="E20" s="4" t="n">
+      <c r="E20" s="5" t="n">
         <v>-8.60204081632654</v>
       </c>
-      <c r="F20" s="4" t="n">
+      <c r="F20" s="5" t="n">
         <v>6.6600185528757</v>
       </c>
-      <c r="G20" s="4" t="n">
+      <c r="G20" s="5" t="n">
         <v>6.60363355076099</v>
       </c>
-      <c r="H20" s="4" t="n">
+      <c r="H20" s="5" t="n">
         <v>-2.14415584415585</v>
       </c>
-      <c r="I20" s="4" t="n">
+      <c r="I20" s="5" t="n">
         <v>-4.53645418326694</v>
       </c>
-      <c r="J20" s="4" t="n">
+      <c r="J20" s="5" t="n">
         <v>-1.57368421052632</v>
       </c>
-      <c r="K20" s="4" t="n">
+      <c r="K20" s="5" t="n">
         <v>-29.2632307692308</v>
       </c>
-      <c r="L20" s="4" t="n">
+      <c r="L20" s="5" t="n">
         <v>-11.5815340909091</v>
       </c>
-      <c r="M20" s="4" t="n">
+      <c r="M20" s="5" t="n">
         <v>37.5170629954109</v>
       </c>
-      <c r="N20" s="4" t="n">
+      <c r="N20" s="5" t="n">
         <v>-27.6304753028891</v>
       </c>
-      <c r="O20" s="4" t="n">
+      <c r="O20" s="5" t="n">
         <v>-42.7464612421762</v>
       </c>
     </row>
@@ -1201,46 +1222,46 @@
       <c r="A21" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="B21" s="4" t="n">
+      <c r="B21" s="5" t="n">
         <v>-12.9560675074054</v>
       </c>
-      <c r="C21" s="4" t="n">
+      <c r="C21" s="5" t="n">
         <v>-17.8082442541281</v>
       </c>
-      <c r="D21" s="4" t="n">
+      <c r="D21" s="5" t="n">
         <v>-10.419526874976</v>
       </c>
-      <c r="E21" s="4" t="n">
+      <c r="E21" s="5" t="n">
         <v>0.480071452495268</v>
       </c>
-      <c r="F21" s="4" t="n">
+      <c r="F21" s="5" t="n">
         <v>-11.9843102466092</v>
       </c>
-      <c r="G21" s="4" t="n">
+      <c r="G21" s="5" t="n">
         <v>-26.5512402764036</v>
       </c>
-      <c r="H21" s="4" t="n">
+      <c r="H21" s="5" t="n">
         <v>-11.4596269170318</v>
       </c>
-      <c r="I21" s="4" t="n">
+      <c r="I21" s="5" t="n">
         <v>0.161301429176586</v>
       </c>
-      <c r="J21" s="4" t="n">
+      <c r="J21" s="5" t="n">
         <v>4.84916922760763</v>
       </c>
-      <c r="K21" s="4" t="n">
+      <c r="K21" s="5" t="n">
         <v>27.0147828677937</v>
       </c>
-      <c r="L21" s="4" t="n">
+      <c r="L21" s="5" t="n">
         <v>13.4198494375597</v>
       </c>
-      <c r="M21" s="4" t="n">
+      <c r="M21" s="5" t="n">
         <v>-37.2626873169909</v>
       </c>
-      <c r="N21" s="4" t="n">
+      <c r="N21" s="5" t="n">
         <v>57.560928495541</v>
       </c>
-      <c r="O21" s="4" t="n">
+      <c r="O21" s="5" t="n">
         <v>46.1540790274783</v>
       </c>
     </row>
@@ -1248,46 +1269,46 @@
       <c r="A22" s="3" t="s">
         <v>35</v>
       </c>
-      <c r="B22" s="4" t="n">
+      <c r="B22" s="5" t="n">
         <v>-18.4397163120567</v>
       </c>
-      <c r="C22" s="4" t="n">
+      <c r="C22" s="5" t="n">
         <v>-6.90423162583519</v>
       </c>
-      <c r="D22" s="4" t="n">
+      <c r="D22" s="5" t="n">
         <v>15.6424581005587</v>
       </c>
-      <c r="E22" s="4" t="n">
+      <c r="E22" s="5" t="n">
         <v>-7.40740740740741</v>
       </c>
-      <c r="F22" s="4" t="n">
+      <c r="F22" s="5" t="n">
         <v>26.1857707509881</v>
       </c>
-      <c r="G22" s="4" t="n">
+      <c r="G22" s="5" t="n">
         <v>33.0289437146214</v>
       </c>
-      <c r="H22" s="4" t="n">
+      <c r="H22" s="5" t="n">
         <v>-2.78372591006424</v>
       </c>
-      <c r="I22" s="4" t="n">
+      <c r="I22" s="5" t="n">
         <v>16.4583333333333</v>
       </c>
-      <c r="J22" s="4" t="n">
+      <c r="J22" s="5" t="n">
         <v>-10.3</v>
       </c>
-      <c r="K22" s="4" t="n">
+      <c r="K22" s="5" t="n">
         <v>-10.4452054794521</v>
       </c>
-      <c r="L22" s="4" t="n">
+      <c r="L22" s="5" t="n">
         <v>-40.0377714825307</v>
       </c>
-      <c r="M22" s="4" t="n">
+      <c r="M22" s="5" t="n">
         <v>-17.4564796905222</v>
       </c>
-      <c r="N22" s="4" t="n">
+      <c r="N22" s="5" t="n">
         <v>-39.6403759705762</v>
       </c>
-      <c r="O22" s="4" t="n">
+      <c r="O22" s="5" t="n">
         <v>-11.6225546605294</v>
       </c>
     </row>
@@ -1295,46 +1316,46 @@
       <c r="A23" s="3" t="s">
         <v>36</v>
       </c>
-      <c r="B23" s="4" t="n">
+      <c r="B23" s="5" t="n">
         <v>-2.89666666666666</v>
       </c>
-      <c r="C23" s="4" t="n">
+      <c r="C23" s="5" t="n">
         <v>2.97093301435407</v>
       </c>
-      <c r="D23" s="4" t="n">
+      <c r="D23" s="5" t="n">
         <v>-18.5858293075684</v>
       </c>
-      <c r="E23" s="4" t="n">
+      <c r="E23" s="5" t="n">
         <v>-6.616</v>
       </c>
-      <c r="F23" s="4" t="n">
+      <c r="F23" s="5" t="n">
         <v>-4.89091620986688</v>
       </c>
-      <c r="G23" s="4" t="n">
+      <c r="G23" s="5" t="n">
         <v>-3.73337481433905</v>
       </c>
-      <c r="H23" s="4" t="n">
+      <c r="H23" s="5" t="n">
         <v>-2.88766519823789</v>
       </c>
-      <c r="I23" s="4" t="n">
+      <c r="I23" s="5" t="n">
         <v>-10.0227191413238</v>
       </c>
-      <c r="J23" s="4" t="n">
+      <c r="J23" s="5" t="n">
         <v>22.1089186176143</v>
       </c>
-      <c r="K23" s="4" t="n">
+      <c r="K23" s="5" t="n">
         <v>-8.59273422562141</v>
       </c>
-      <c r="L23" s="4" t="n">
+      <c r="L23" s="5" t="n">
         <v>50.1505511811024</v>
       </c>
-      <c r="M23" s="4" t="n">
+      <c r="M23" s="5" t="n">
         <v>-8.51939074399532</v>
       </c>
-      <c r="N23" s="4" t="n">
+      <c r="N23" s="5" t="n">
         <v>-3.26012186865268</v>
       </c>
-      <c r="O23" s="4" t="n">
+      <c r="O23" s="5" t="n">
         <v>-8.55520833333333</v>
       </c>
     </row>
@@ -1342,85 +1363,104 @@
       <c r="A24" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="B24" s="4" t="n">
+      <c r="B24" s="5" t="n">
         <v>-9.852495399343</v>
       </c>
-      <c r="C24" s="4" t="n">
+      <c r="C24" s="5" t="n">
         <v>-1.37505706655267</v>
       </c>
-      <c r="D24" s="4" t="n">
+      <c r="D24" s="5" t="n">
         <v>2.8517629187748</v>
       </c>
-      <c r="E24" s="4" t="n">
+      <c r="E24" s="5" t="n">
         <v>13.9381478625889</v>
       </c>
-      <c r="F24" s="4" t="n">
+      <c r="F24" s="5" t="n">
         <v>-16.9234848004558</v>
       </c>
-      <c r="G24" s="4" t="n">
+      <c r="G24" s="5" t="n">
         <v>-14.2653850787326</v>
       </c>
-      <c r="H24" s="4" t="n">
+      <c r="H24" s="5" t="n">
         <v>-3.37725963392229</v>
       </c>
-      <c r="I24" s="4" t="n">
+      <c r="I24" s="5" t="n">
         <v>-8.1461629153056</v>
       </c>
-      <c r="J24" s="4" t="n">
+      <c r="J24" s="5" t="n">
         <v>-8.51963404201707</v>
       </c>
-      <c r="K24" s="4" t="n">
+      <c r="K24" s="5" t="n">
         <v>15.0483202945237</v>
       </c>
-      <c r="L24" s="4" t="n">
+      <c r="L24" s="5" t="n">
         <v>-7.70418351764528</v>
       </c>
-      <c r="M24" s="4" t="n">
+      <c r="M24" s="5" t="n">
         <v>18.2780963310096</v>
       </c>
-      <c r="N24" s="4" t="n">
+      <c r="N24" s="5" t="n">
         <v>49.771004333561</v>
       </c>
-      <c r="O24" s="4" t="n">
+      <c r="O24" s="5" t="n">
         <v>22.1707086470662</v>
       </c>
     </row>
-    <row r="25" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="5" t="s">
+    <row r="25" customFormat="false" ht="12.8" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A25" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="B25" s="5"/>
-      <c r="C25" s="5"/>
-      <c r="D25" s="5"/>
-      <c r="E25" s="5"/>
-      <c r="F25" s="5"/>
-      <c r="G25" s="5"/>
-      <c r="H25" s="5"/>
-      <c r="I25" s="5"/>
-      <c r="J25" s="5"/>
-      <c r="K25" s="5"/>
-      <c r="L25" s="5"/>
-      <c r="M25" s="5"/>
-      <c r="N25" s="5"/>
-      <c r="O25" s="5"/>
-      <c r="P25" s="5"/>
-      <c r="Q25" s="5"/>
-      <c r="R25" s="5"/>
-      <c r="S25" s="5"/>
-      <c r="T25" s="5"/>
-      <c r="U25" s="5"/>
-      <c r="V25" s="5"/>
-      <c r="W25" s="5"/>
-      <c r="X25" s="5"/>
-      <c r="Y25" s="5"/>
-      <c r="Z25" s="5"/>
-      <c r="AA25" s="5"/>
-      <c r="AB25" s="5"/>
-    </row>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="B25" s="6"/>
+      <c r="C25" s="6"/>
+      <c r="D25" s="6"/>
+      <c r="E25" s="6"/>
+      <c r="F25" s="6"/>
+      <c r="G25" s="6"/>
+      <c r="H25" s="6"/>
+      <c r="I25" s="6"/>
+      <c r="J25" s="6"/>
+      <c r="K25" s="6"/>
+      <c r="L25" s="6"/>
+      <c r="M25" s="6"/>
+      <c r="N25" s="6"/>
+      <c r="O25" s="6"/>
+    </row>
+    <row r="26" customFormat="false" ht="14.4" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
+      <c r="A26" s="7" t="s">
+        <v>39</v>
+      </c>
+      <c r="B26" s="7"/>
+      <c r="C26" s="7"/>
+      <c r="D26" s="7"/>
+      <c r="E26" s="7"/>
+      <c r="F26" s="7"/>
+      <c r="G26" s="7"/>
+      <c r="H26" s="7"/>
+      <c r="I26" s="7"/>
+      <c r="J26" s="7"/>
+      <c r="K26" s="7"/>
+      <c r="L26" s="7"/>
+      <c r="M26" s="7"/>
+      <c r="N26" s="7"/>
+      <c r="O26" s="7"/>
+      <c r="P26" s="8"/>
+      <c r="Q26" s="8"/>
+      <c r="R26" s="8"/>
+      <c r="S26" s="8"/>
+      <c r="T26" s="8"/>
+      <c r="U26" s="8"/>
+      <c r="V26" s="8"/>
+      <c r="W26" s="8"/>
+      <c r="X26" s="8"/>
+      <c r="Y26" s="8"/>
+      <c r="Z26" s="8"/>
+      <c r="AA26" s="8"/>
+      <c r="AB26" s="8"/>
+    </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A25:AB25"/>
+  <mergeCells count="2">
+    <mergeCell ref="A25:O25"/>
+    <mergeCell ref="A26:O26"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/agriculture 18.xlsx
+++ b/agriculture 18.xlsx
@@ -136,7 +136,7 @@
     <t xml:space="preserve"> 2019-20</t>
   </si>
   <si>
-    <t xml:space="preserve">Unit:- </t>
+    <t xml:space="preserve">Unit:- Percentage (%)</t>
   </si>
   <si>
     <t xml:space="preserve">Source: Directorate of Economics and Statistics (1997-2020)</t>
@@ -151,7 +151,7 @@
     <numFmt numFmtId="165" formatCode="[$-409]0;\(0\)"/>
     <numFmt numFmtId="166" formatCode="0.00"/>
   </numFmts>
-  <fonts count="7">
+  <fonts count="6">
     <font>
       <sz val="10"/>
       <name val="Arial"/>
@@ -179,12 +179,6 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Arial"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -250,7 +244,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -283,10 +277,6 @@
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
       <protection locked="false" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false" readingOrder="1"/>
-      <protection locked="false" hidden="false"/>
-    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -305,7 +295,7 @@
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
   <dimension ref="A1:AB26"/>
-  <sheetFormatPr defaultColWidth="10.796875" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
+  <sheetFormatPr defaultColWidth="10.8125" defaultRowHeight="14.4" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
@@ -1443,19 +1433,19 @@
       <c r="M26" s="7"/>
       <c r="N26" s="7"/>
       <c r="O26" s="7"/>
-      <c r="P26" s="8"/>
-      <c r="Q26" s="8"/>
-      <c r="R26" s="8"/>
-      <c r="S26" s="8"/>
-      <c r="T26" s="8"/>
-      <c r="U26" s="8"/>
-      <c r="V26" s="8"/>
-      <c r="W26" s="8"/>
-      <c r="X26" s="8"/>
-      <c r="Y26" s="8"/>
-      <c r="Z26" s="8"/>
-      <c r="AA26" s="8"/>
-      <c r="AB26" s="8"/>
+      <c r="P26" s="7"/>
+      <c r="Q26" s="7"/>
+      <c r="R26" s="7"/>
+      <c r="S26" s="7"/>
+      <c r="T26" s="7"/>
+      <c r="U26" s="7"/>
+      <c r="V26" s="7"/>
+      <c r="W26" s="7"/>
+      <c r="X26" s="7"/>
+      <c r="Y26" s="7"/>
+      <c r="Z26" s="7"/>
+      <c r="AA26" s="7"/>
+      <c r="AB26" s="7"/>
     </row>
   </sheetData>
   <mergeCells count="2">
